--- a/artfynd/A 30064-2026 artfynd.xlsx
+++ b/artfynd/A 30064-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136481710</v>
       </c>
       <c r="B4" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30064-2026 artfynd.xlsx
+++ b/artfynd/A 30064-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136481710</v>
       </c>
       <c r="B4" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30064-2026 artfynd.xlsx
+++ b/artfynd/A 30064-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481819</v>
       </c>
       <c r="B2" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136481820</v>
       </c>
       <c r="B3" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136481710</v>
       </c>
       <c r="B4" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136481845</v>
       </c>
       <c r="B5" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136481755</v>
       </c>
       <c r="B6" t="n">
-        <v>80368</v>
+        <v>80370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Robert Sandberg</t>
+          <t>Robert Sandberg, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 30064-2026 artfynd.xlsx
+++ b/artfynd/A 30064-2026 artfynd.xlsx
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Robert Sandberg, Tyr Nilsson</t>
+          <t>Tyr Nilsson, Robert Sandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 30064-2026 artfynd.xlsx
+++ b/artfynd/A 30064-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136481710</v>
       </c>
       <c r="B4" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30064-2026 artfynd.xlsx
+++ b/artfynd/A 30064-2026 artfynd.xlsx
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Robert Sandberg</t>
+          <t>Robert Sandberg, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 30064-2026 artfynd.xlsx
+++ b/artfynd/A 30064-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481819</v>
       </c>
       <c r="B2" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136481820</v>
       </c>
       <c r="B3" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136481710</v>
       </c>
       <c r="B4" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Robert Sandberg</t>
+          <t>Robert Sandberg, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -989,7 +989,7 @@
         <v>136481845</v>
       </c>
       <c r="B5" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136481755</v>
       </c>
       <c r="B6" t="n">
-        <v>80370</v>
+        <v>80374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30064-2026 artfynd.xlsx
+++ b/artfynd/A 30064-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481819</v>
       </c>
       <c r="B2" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136481820</v>
       </c>
       <c r="B3" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136481710</v>
       </c>
       <c r="B4" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Robert Sandberg, Tyr Nilsson</t>
+          <t>Tyr Nilsson, Robert Sandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -989,7 +989,7 @@
         <v>136481845</v>
       </c>
       <c r="B5" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136481755</v>
       </c>
       <c r="B6" t="n">
-        <v>80374</v>
+        <v>80376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30064-2026 artfynd.xlsx
+++ b/artfynd/A 30064-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481819</v>
       </c>
       <c r="B2" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136481820</v>
       </c>
       <c r="B3" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136481710</v>
       </c>
       <c r="B4" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136481845</v>
       </c>
       <c r="B5" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136481755</v>
       </c>
       <c r="B6" t="n">
-        <v>80376</v>
+        <v>80377</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30064-2026 artfynd.xlsx
+++ b/artfynd/A 30064-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136481710</v>
       </c>
       <c r="B4" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30064-2026 artfynd.xlsx
+++ b/artfynd/A 30064-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481819</v>
       </c>
       <c r="B2" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136481820</v>
       </c>
       <c r="B3" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136481710</v>
       </c>
       <c r="B4" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136481845</v>
       </c>
       <c r="B5" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136481755</v>
       </c>
       <c r="B6" t="n">
-        <v>80377</v>
+        <v>80379</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
